--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,270 +468,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Data Lake, Kinesis, CI/CD, Git</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b41d24203ba44f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AmeriSave Mortgage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Mistral, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2de324eee580b25</t>
+          <t>https://www.indeed.com/viewjob?jk=f634b4ab70d69f90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Systems Software Engineer, E-commerce AI Platform - GeForce NOW</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bfab57854e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=da0268326a099b77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tech Anchor</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Kafka, PostgreSQL, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4680a73e3d8aea7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, NoSQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de97150c606b641</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6d6e4bff6acbda</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Platform Integrations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Twelve Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, FastAPI, Docker, Kubernetes, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c7921fb0550ee</t>
+          <t>https://www.indeed.com/viewjob?jk=de9fdeb4d1c2f418</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software EngineerÂ - AI/ML</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21fc199087599f0</t>
+          <t>https://www.indeed.com/viewjob?jk=251ab2b4fe250967</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,487 +741,487 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29d9e05a38a90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menarini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Databricks, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4735c396f39ae2f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c41abc30f36a94cc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (hybrid onsite, Omaha NE)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FNBO - First National Bank of Omaha</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9644ef646443f544</t>
+          <t>https://www.indeed.com/viewjob?jk=fc18d2c932f87262</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Redshift, Data Lake, CI/CD, Git, Redshift, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=b61165b09dc15b48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f33e21619692acd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BioIntellisense</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f3c57f8e963160</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c95c37baddc933</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cab45495358458c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a4f92733ae0f00</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6070389e103495</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IP Methodology and Automation Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5916115c591c8d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f83ec2a54fa3dad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Avita Care Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c837dde9f104de88</t>
+          <t>https://www.indeed.com/viewjob?jk=23ddceb84dc7ba33</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Java/Retail POS</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, AKS, CI/CD, Git, Databricks, Kafka, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c23d584338e9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0b37af7b772907</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Java/Retail POS</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, AKS, CI/CD, Git, Databricks, Kafka, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f62fd5be4e1824</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8dc954827abd36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Java/Retail POS</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, AKS, CI/CD, Git, Databricks, Kafka, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf75ebb17b4f23c</t>
+          <t>https://www.indeed.com/viewjob?jk=e424ea056f613fa8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Java/Retail POS</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, AKS, CI/CD, Git, Databricks, Kafka, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774ced732d07198d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d921c90cdd34290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer (Onsite Hybrid)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,287 +1231,1232 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1bca275295d625</t>
+          <t>https://www.indeed.com/viewjob?jk=9584ce624d6a847c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist PennDnA</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Penn Medicine</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215b935808996874</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bbca0b955f7e3d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Massachusetts</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hingham, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d156854dd429e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e9399b3f2ca167</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Massachusetts</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hingham, MA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4391f1e862218993</t>
+          <t>https://www.indeed.com/viewjob?jk=6f80645f01363206</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Product Owner</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Massachusetts</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863e92ea49a1b65b</t>
+          <t>https://www.indeed.com/viewjob?jk=291e92edf7c14075</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2388d9f0f950ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0c7742fa7a01f129</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRUSOE</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d47e54455c534f</t>
+          <t>https://www.indeed.com/viewjob?jk=671c6d13e513d7f0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer (L3)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, NoSQL, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8fce9d5bc7f06f</t>
+          <t>https://www.indeed.com/viewjob?jk=937d4aba18a16d77</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior ML Operations (MLOps) Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b5100e2c95c3a17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ceb73dfb3dc698a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e6823cb9f7a8547</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99568d10e0e02b48</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=358e73fd136e29cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e41d3d630caa388</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc87c66bc77f963c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1afc6e01fbd824c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c7dc490f0c9920f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0da052d6975aba64</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2756528dd5202908</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=053bc6cc2f377494</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a39fce46cb14ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69f0f8a3f2317fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2ffc2d688ac6188</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aa74fcd5c01cf38</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75bf488e82874c4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbee1519ba0e768c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9051d80a4d4dd546</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b675d1f3463d8c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb09d7d6027a064e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git, BigQuery, Kafka</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbc075b687c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, AI Search - USDS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a1544bfe30d14cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, SambaSuite Platform</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Kinesis, CI/CD, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Dataflow, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1beb4134de9fdc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4add9c22eff2aac0</t>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=946c891d4fdb97c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DevOps Engineer – Infrastructure as Code (IaC)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19b4b603548ea27c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SE-AI</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CLOUDSUFI</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, FastAPI, Docker, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Redshift, BigQuery, Synapse</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7588676e4b241a8</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>RAG, Data Lake, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bf78184131549d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>AI Systems Engineer (OpenClaw / Automation / DevOps)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Databricks, Matplotlib, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=8e05c881b8548e84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Storage, Search, &amp; Data Platforms</t>
+          <t>Software Engineer, New College Grad - 2026, Atlanta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1800b3c8810aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=d93df3e7b5517b95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Storage, Search, &amp; Data Platforms</t>
+          <t>Software Engineer, New College Grad - 2026, Highlands Ranch, CO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e4545d6858ad8f</t>
+          <t>https://www.indeed.com/viewjob?jk=42391d5c41880a67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Storage, Search, &amp; Data Platforms</t>
+          <t>Software Engineer, New College Grad - 2026, Bellevue, WA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4dac74825060f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d50018a74a1e91a4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Storage, Search, &amp; Data Platforms</t>
+          <t>Software Engineer, New College Grad - 2026, Foster City</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, S3, Data Lake, Kafka, MySQL, Cassandra, NoSQL, SQL, R</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e182b7730b18ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1a3ec2535d29a6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior CI/CD Platform Engineer</t>
+          <t>Software Engineer, New College Grad - 2026, Austin, TX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a7c55f916bd0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec8bac87a9e320</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applied AI ML Engineer-Sr. Associate</t>
+          <t>Data Scientist Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdcd481bb65ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40b84f045800ac</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Card Data Analytics</t>
+          <t>Data Scientist Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc323f0ca9cc5f0</t>
+          <t>https://www.indeed.com/viewjob?jk=09deb759b3af5090</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Architect / Data Scientist</t>
+          <t>Software Quality Engineer - San Jose, CA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Elekta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75909ef7a8cd4059</t>
+          <t>https://www.indeed.com/viewjob?jk=8af71e9cc8f145e5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Contract)</t>
+          <t>MLOps engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1d8fcacc8afbce</t>
+          <t>https://www.indeed.com/viewjob?jk=738683bfcbbfefdb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist - Corporate &amp; Institutional Banking</t>
+          <t>Machine Learning Engineer- AI Data Platform (Minneapolis, MN)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>MOBE LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, AWS SageMaker, MLflow, Apache Airflow, Git, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,77 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e943e48c3231f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ea5cc55750c700</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer- AI Data Platform (Reno, NV)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MOBE LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Reno, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, AWS SageMaker, MLflow, Apache Airflow, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7188b184a382ca79</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist, New College Grad - 2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9ac059c9ef24f3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Redshift, BigQuery, Synapse</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf2652e8399caea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc91885a86b9bf62</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Systems Engineer (OpenClaw / Automation / DevOps)</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e05c881b8548e84</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2026, Atlanta</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93df3e7b5517b95</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2026, Highlands Ranch, CO</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42391d5c41880a67</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2026, Bellevue, WA</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50018a74a1e91a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2026, Foster City</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1a3ec2535d29a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2026, Austin, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,252 +741,77 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec8bac87a9e320</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist Intern</t>
+          <t>AI Hardware Design Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40b84f045800ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1f9f283673c25287</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist Intern</t>
+          <t>Fircosoft Software Engineer – Screening/ V5/V6/ CONTINUITY- Jersey City, NJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>RSHARMA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Kubernetes, CI/CD, Jenkins, Kafka, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09deb759b3af5090</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer - San Jose, CA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Elekta</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af71e9cc8f145e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MLOps engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=738683bfcbbfefdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer- AI Data Platform (Minneapolis, MN)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MOBE LLC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, AWS SageMaker, MLflow, Apache Airflow, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ea5cc55750c700</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer- AI Data Platform (Reno, NV)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MOBE LLC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Reno, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, AWS SageMaker, MLflow, Apache Airflow, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7188b184a382ca79</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist, New College Grad - 2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9ac059c9ef24f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a95ea7e83fc5317a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf2652e8399caea</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0a5e2d2df190d1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Python</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc91885a86b9bf62</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, CI/CD, Snowflake, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=9310b61a075b3d43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer, Front End</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, R</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=8e234c4107203ba8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Scaled Insights Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=33fefb12826bbb7c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Hardware Design Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+          <t>RAG, Gemini, Copilot, S3, EC2, CI/CD, Terraform, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,217 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9f283673c25287</t>
+          <t>https://www.indeed.com/viewjob?jk=64863740ef3aaa0c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fircosoft Software Engineer – Screening/ V5/V6/ CONTINUITY- Jersey City, NJ</t>
+          <t>Sr. Managed Services Engineer - AI &amp; Copilot</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RSHARMA</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Glue, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08d8f77f51717e3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Kafka, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65694c78907e4884</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Kafka, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a95ea7e83fc5317a</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, Git, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80366ebbb35a4613</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Platform Team)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=474909faf3a687cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AIP Innovation Engineer - iDEA by Lear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lear Corporation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, MLflow, CI/CD, Git, PySpark, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fc9f3f7dcd2d067</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Technical Recruiter - AI Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0a5e2d2df190d1</t>
+          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>AI Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
+          <t>RAG, LLaMA, Copilot, Mistral, Hugging Face, Prompt Engineering, AWS SageMaker, Docker, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1ff8d1d924b4328</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>AI Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, LLaMA, Copilot, Mistral, Hugging Face, Prompt Engineering, AWS SageMaker, Docker, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=763057b0de0afef0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, TensorFlow, PyTorch, FastAPI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
+          <t>https://www.indeed.com/viewjob?jk=36204bb82af327a4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, CI/CD, Snowflake, R</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Redshift, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9310b61a075b3d43</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Redshift, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Front End</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Redshift, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e234c4107203ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scaled Insights Associate</t>
+          <t>Senior AI Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33fefb12826bbb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd39cdcd0dcfdf4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, S3, EC2, CI/CD, Terraform, MongoDB, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64863740ef3aaa0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3795cef4707d618</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Managed Services Engineer - AI &amp; Copilot</t>
+          <t>Senior Data Scientist (Retail)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Glue, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d8f77f51717e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c7f8b6f85b4348a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Kafka, R, Java, Scala, Optimization</t>
+          <t>RAG, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65694c78907e4884</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Kubernetes, Git, BigQuery, Python, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80366ebbb35a4613</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+          <t>https://www.indeed.com/viewjob?jk=e84cba60aad22235</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Platform Team)</t>
+          <t>Product Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,532 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474909faf3a687cb</t>
+          <t>https://www.indeed.com/viewjob?jk=acef5e7b10ed81f9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AIP Innovation Engineer - iDEA by Lear</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lear Corporation</t>
+          <t>Communify</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=883c72c9a26291e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fe818cf3e82b216</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7367f68be79f1c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HR Technology Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb2cf6e8c2dd600a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Git, Tableau, Python, SQL, R, Java, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28251f59b3e0eabf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Git, Tableau, Python, SQL, R, Java, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2988fd782a6fa358</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Defense Unicorns</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, MLflow, CI/CD, Git, PySpark, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc9f3f7dcd2d067</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Redshift, Data Lake, Snowflake, Databricks, Redshift, PySpark, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9a988d25e3d08c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Technical Recruiter - Engineering</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BigQuery, AKS, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1805085c02c68912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI / Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Calix</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80196e9a7cb4f25a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ADMINISTRATOR L3(CONTRACT)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec793bd736187f41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GEN AI Sr Data Scientist/Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c6673ee0c786bd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GEN AI Sr Data Scientist/Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ccf8c51daaa305a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GEN AI Sr Data Scientist/Data Scientist</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd5b3c82500307b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GEN AI Sr Data Scientist/Data Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c195dcf8101f11ea</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technical Recruiter - AI Engineering</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering, PyTorch</t>
+          <t>Gemini, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Remote</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Copilot, Mistral, Hugging Face, Prompt Engineering, AWS SageMaker, Docker, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, RAG, LightGBM, CatBoost, S3, Docker, CI/CD, Jenkins, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1ff8d1d924b4328</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Remote</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Copilot, Mistral, Hugging Face, Prompt Engineering, AWS SageMaker, Docker, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763057b0de0afef0</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, TensorFlow, PyTorch, FastAPI, CI/CD, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MySQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36204bb82af327a4</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Redshift, PostgreSQL, Python</t>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Redshift, PostgreSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, Databricks, MySQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Aires</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Redshift, PostgreSQL, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=24a00011c009f4a8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (USA - Remote)</t>
+          <t>Sr. Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Docker, CI/CD, Python, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd39cdcd0dcfdf4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (USA - Remote)</t>
+          <t>Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Docker, CI/CD, Python, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3795cef4707d618</t>
+          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (Retail)</t>
+          <t>Senior Data Scientist - Computer Vision &amp; ML, Cross-Domain AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, PyTorch, OpenCV, MLflow, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c7f8b6f85b4348a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e921e7d4837b76</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
+          <t>https://www.indeed.com/viewjob?jk=280d17d7ae0d5ba7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Kafka, Python, R, Java</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca88ace015b92141</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Senior Data Scientist, Cross-Domain AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e84cba60aad22235</t>
+          <t>https://www.indeed.com/viewjob?jk=bac2d5fba0522541</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Software Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure &amp; BSP, Cygnus team</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acef5e7b10ed81f9</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee510a91c5bd78</t>
         </is>
       </c>
     </row>
@@ -963,20 +963,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Communify</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Hebron, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,497 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=883c72c9a26291e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe818cf3e82b216</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7367f68be79f1c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>HR Technology Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2cf6e8c2dd600a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Git, Tableau, Python, SQL, R, Java, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28251f59b3e0eabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Git, Tableau, Python, SQL, R, Java, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2988fd782a6fa358</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Conagra Brands</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Redshift, Data Lake, Snowflake, Databricks, Redshift, PySpark, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a988d25e3d08c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Technical Recruiter - Engineering</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Sigma Computing</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>BigQuery, AKS, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1805085c02c68912</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI / Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Calix</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80196e9a7cb4f25a</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ADMINISTRATOR L3(CONTRACT)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec793bd736187f41</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>GEN AI Sr Data Scientist/Data Scientist</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6673ee0c786bd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>GEN AI Sr Data Scientist/Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ccf8c51daaa305a</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>GEN AI Sr Data Scientist/Data Scientist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5b3c82500307b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>GEN AI Sr Data Scientist/Data Scientist</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c195dcf8101f11ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7654182be4b0187e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-07.xlsx
+++ b/daily_matches/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gemini, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, S3, Glue, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LightGBM, CatBoost, S3, Docker, CI/CD, Jenkins, Git, Snowflake</t>
+          <t>RAG, S3, Glue, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery</t>
+          <t>RAG, S3, Glue, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MySQL, Python</t>
+          <t>AI Engineer, RAG, ChromaDB, Prompt Engineering, FastAPI, Docker, Git, Snowflake, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Java AI Engineer | Charlotte, NC, USA (3 days onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e036639932b33a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, Databricks, MySQL, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a00011c009f4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Cloud/Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Integrity Marketing Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, Snowflake, PySpark, Dask, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4b528d73f04fa196</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud/Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Computer Vision &amp; ML, Cross-Domain AI</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, OpenCV, MLflow, CI/CD, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Git, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e921e7d4837b76</t>
+          <t>https://www.indeed.com/viewjob?jk=c781c493dccbef55</t>
         </is>
       </c>
     </row>
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280d17d7ae0d5ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bb30b9ffd0c178</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Ground Data Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, R, Java, Scala</t>
+          <t>RAG, Dataflow, Git, Hadoop, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca88ace015b92141</t>
+          <t>https://www.indeed.com/viewjob?jk=25d39fcce644a309</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cross-Domain AI</t>
+          <t>Senior Data / Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Thia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2d5fba0522541</t>
+          <t>https://www.indeed.com/viewjob?jk=d76fc6c5b5ddda26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure &amp; BSP, Cygnus team</t>
+          <t>Marketing Data Scientist Senior Associate - Consumer Bank</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee510a91c5bd78</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Indiana University Health</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hebron, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7654182be4b0187e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9dedb2414c77aea</t>
         </is>
       </c>
     </row>
